--- a/backend/sample_data/演示素材/演示客户数据.xlsx
+++ b/backend/sample_data/演示素材/演示客户数据.xlsx
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>王强</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>蓝海科技有限公司</t>
+          <t>XX科技有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>wangqiang@lanhai.example</t>
+          <t>zhangsan@example.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -483,12 +483,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>李梅</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>远大智能制造</t>
+          <t>XX制造公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>limei@yuanda.example</t>
+          <t>lisi@example.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>陈杰</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>华信贸易集团</t>
+          <t>XX贸易公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>chenjie@huaxin.example</t>
+          <t>wangwu@example.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -547,12 +547,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>赵琳</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>宏图建筑</t>
+          <t>XX建筑公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>zhaolin@hongtu.example</t>
+          <t>zhaoliu@example.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
